--- a/analysis/tables/pythia-2.8b.xlsx
+++ b/analysis/tables/pythia-2.8b.xlsx
@@ -536,27 +536,27 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.8768497055426921</v>
+        <v>0.637177452694356</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.1667529072778909</v>
+        <v>-0.07322227202000367</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>y = 0.877x - 0.167</t>
+          <t>y = 0.637x - 0.073</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0.8446767808088257</v>
+        <v>0.8446767808088249</v>
       </c>
       <c r="H3" t="n">
         <v>0.07505040202274707</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1901727356738812</v>
+        <v>0.1149166087255244</v>
       </c>
       <c r="J3" t="n">
-        <v>0.7100967982648012</v>
+        <v>0.5639551806743524</v>
       </c>
       <c r="K3" t="n">
         <v>0.1471454226195276</v>
@@ -577,27 +577,27 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.869416747179116</v>
+        <v>0.6354342967558725</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.08176119931705486</v>
+        <v>-0.06729657450078017</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>y = 0.869x - 0.082</t>
+          <t>y = 0.635x - 0.067</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0.8662664386832915</v>
+        <v>0.8482410639547229</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0742145230747908</v>
+        <v>0.07491240496584443</v>
       </c>
       <c r="I4" t="n">
-        <v>0.09404143591935035</v>
+        <v>0.1059064246993814</v>
       </c>
       <c r="J4" t="n">
-        <v>0.7876555478620612</v>
+        <v>0.5681377222550923</v>
       </c>
       <c r="K4" t="n">
         <v>0.1471454226195276</v>
